--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92563866863</v>
+        <v>46157.9308212058</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9308212058</v>
+        <v>46157.93161208522</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93161208522</v>
+        <v>46157.93395764427</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93395764427</v>
+        <v>46157.93712840463</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93712840463</v>
+        <v>46158.2821245586</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2821245586</v>
+        <v>46158.29673610294</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29673610294</v>
+        <v>46158.29809453982</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29809453982</v>
+        <v>46158.33383247247</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33383247247</v>
+        <v>46158.36851515704</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36851515704</v>
+        <v>46158.37283481418</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
